--- a/agent/docs/agent-management-sheet-v3.xlsx
+++ b/agent/docs/agent-management-sheet-v3.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Workflow Catalog" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Workflow Steps" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Workflow Routes" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Workflow Data Schema" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Step Data Mapping" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contract Registry" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contract Mapping" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enum Registry" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Workflow Catalog" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Workflow Steps" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Workflow Routes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Workflow Data Schema" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Step Data Mapping" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Contract Registry" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Contract Mapping" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Enum Registry" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workflow Catalog'!$A$1:$L$10</definedName>
@@ -7174,12 +7174,12 @@
       <c r="L80" s="3" t="inlineStr"/>
       <c r="M80" s="3" t="inlineStr">
         <is>
-          <t>from_account_hint, from_account_id, account_resolution_outcome, accounts, account_selection_outcome, amount_input_outcome, input_request_id, confirmation_id, confirmation_view, approval_outcome, change_target, correction_selection_outcome, blocked_view, auth_context_id, auth_request_view, auth_status, auth_retry_outcome, auth_attempt</t>
+          <t>from_account_hint, from_account_id, account_resolution_outcome, accounts, account_selection_outcome, amount_input_outcome, input_request_id, confirmation_id, confirmation_view, approval_outcome, change_target, option_selection_outcome, blocked_view, auth_context_id, auth_request_view, auth_status, auth_attempt</t>
         </is>
       </c>
       <c r="N80" s="3" t="inlineStr">
         <is>
-          <t>from_account_hint, from_account_id, account_resolution_outcome, accounts, account_selection_outcome, amount_input_outcome, input_request_id, confirmation_id, confirmation_view, approval_outcome, change_target, correction_selection_outcome, blocked_view, auth_context_id, auth_request_view, auth_status, auth_retry_outcome, auth_attempt</t>
+          <t>from_account_hint, from_account_id, account_resolution_outcome, accounts, account_selection_outcome, amount_input_outcome, input_request_id, confirmation_id, confirmation_view, approval_outcome, change_target, option_selection_outcome, blocked_view, auth_context_id, auth_request_view, auth_status, auth_attempt, option</t>
         </is>
       </c>
       <c r="O80" s="3" t="inlineStr">
@@ -7246,12 +7246,12 @@
       <c r="L81" s="3" t="inlineStr"/>
       <c r="M81" s="3" t="inlineStr">
         <is>
-          <t>to_account_hint, to_account_id, account_resolution_outcome, accounts, account_selection_outcome, amount_input_outcome, input_request_id, confirmation_id, confirmation_view, approval_outcome, change_target, correction_selection_outcome, blocked_view, auth_context_id, auth_request_view, auth_status, auth_retry_outcome, auth_attempt</t>
+          <t>to_account_hint, to_account_id, account_resolution_outcome, accounts, account_selection_outcome, amount_input_outcome, input_request_id, confirmation_id, confirmation_view, approval_outcome, change_target, option_selection_outcome, blocked_view, auth_context_id, auth_request_view, auth_status, auth_attempt</t>
         </is>
       </c>
       <c r="N81" s="3" t="inlineStr">
         <is>
-          <t>to_account_hint, to_account_id, account_resolution_outcome, accounts, account_selection_outcome, amount_input_outcome, input_request_id, confirmation_id, confirmation_view, approval_outcome, change_target, correction_selection_outcome, blocked_view, auth_context_id, auth_request_view, auth_status, auth_retry_outcome, auth_attempt</t>
+          <t>to_account_hint, to_account_id, account_resolution_outcome, accounts, account_selection_outcome, amount_input_outcome, input_request_id, confirmation_id, confirmation_view, approval_outcome, change_target, option_selection_outcome, blocked_view, auth_context_id, auth_request_view, auth_status, auth_attempt, option</t>
         </is>
       </c>
       <c r="O81" s="3" t="inlineStr">
@@ -7318,12 +7318,12 @@
       <c r="L82" s="3" t="inlineStr"/>
       <c r="M82" s="3" t="inlineStr">
         <is>
-          <t>amount, amount_input_outcome, input_request_id, confirmation_id, confirmation_view, approval_outcome, change_target, correction_selection_outcome, blocked_view, auth_context_id, auth_request_view, auth_status, auth_retry_outcome, auth_attempt</t>
+          <t>amount, amount_input_outcome, input_request_id, confirmation_id, confirmation_view, approval_outcome, change_target, option_selection_outcome, blocked_view, auth_context_id, auth_request_view, auth_status, auth_attempt</t>
         </is>
       </c>
       <c r="N82" s="3" t="inlineStr">
         <is>
-          <t>amount, amount_input_outcome, input_request_id, confirmation_id, confirmation_view, approval_outcome, change_target, correction_selection_outcome, blocked_view, auth_context_id, auth_request_view, auth_status, auth_retry_outcome, auth_attempt</t>
+          <t>amount, amount_input_outcome, input_request_id, confirmation_id, confirmation_view, approval_outcome, change_target, option_selection_outcome, blocked_view, auth_context_id, auth_request_view, auth_status, auth_attempt, option</t>
         </is>
       </c>
       <c r="O82" s="3" t="inlineStr">
@@ -7471,7 +7471,7 @@
       </c>
       <c r="N84" s="3" t="inlineStr">
         <is>
-          <t>correction_selection_outcome, change_target, input_request_id</t>
+          <t>option_selection_outcome, option, input_request_id</t>
         </is>
       </c>
       <c r="O84" s="3" t="inlineStr">
@@ -7538,12 +7538,12 @@
       <c r="L85" s="3" t="inlineStr"/>
       <c r="M85" s="3" t="inlineStr">
         <is>
-          <t>auth_context_id, auth_request_view, auth_status, auth_retry_outcome, auth_attempt</t>
+          <t>auth_context_id, auth_request_view, auth_status, option_selection_outcome, auth_attempt</t>
         </is>
       </c>
       <c r="N85" s="3" t="inlineStr">
         <is>
-          <t>auth_context_id, auth_request_view, auth_status, auth_retry_outcome, auth_attempt</t>
+          <t>auth_context_id, auth_request_view, auth_status, option_selection_outcome, auth_attempt</t>
         </is>
       </c>
       <c r="O85" s="3" t="inlineStr">
@@ -7783,7 +7783,7 @@
       </c>
       <c r="N88" s="3" t="inlineStr">
         <is>
-          <t>auth_retry_outcome, input_request_id</t>
+          <t>option_selection_outcome, input_request_id, option</t>
         </is>
       </c>
       <c r="O88" s="3" t="inlineStr">
@@ -8998,12 +8998,12 @@
       <c r="L104" s="3" t="inlineStr"/>
       <c r="M104" s="3" t="inlineStr">
         <is>
-          <t>from_account_hint, account_resolution_outcome, accounts, account_selection_outcome, from_account_id, amount_input_outcome, input_request_id, confirmation_id, confirmation_view, approval_outcome, change_target, correction_selection_outcome, blocked_view, auth_context_id, auth_request_view, auth_status, auth_retry_outcome, auth_attempt</t>
+          <t>from_account_hint, account_resolution_outcome, accounts, account_selection_outcome, from_account_id, amount_input_outcome, input_request_id, confirmation_id, confirmation_view, approval_outcome, change_target, option_selection_outcome, blocked_view, auth_context_id, auth_request_view, auth_status, auth_attempt</t>
         </is>
       </c>
       <c r="N104" s="3" t="inlineStr">
         <is>
-          <t>from_account_hint, account_resolution_outcome, accounts, account_selection_outcome, from_account_id, amount_input_outcome, input_request_id, confirmation_id, confirmation_view, approval_outcome, change_target, correction_selection_outcome, blocked_view, auth_context_id, auth_request_view, auth_status, auth_retry_outcome, auth_attempt</t>
+          <t>from_account_hint, account_resolution_outcome, accounts, account_selection_outcome, from_account_id, amount_input_outcome, input_request_id, confirmation_id, confirmation_view, approval_outcome, change_target, option_selection_outcome, blocked_view, auth_context_id, auth_request_view, auth_status, auth_attempt, option</t>
         </is>
       </c>
       <c r="O104" s="3" t="inlineStr">
@@ -9070,12 +9070,12 @@
       <c r="L105" s="3" t="inlineStr"/>
       <c r="M105" s="3" t="inlineStr">
         <is>
-          <t>recipient_name_hint, recipient_resolution_outcome, recipient_selection_reason, recipient_selection_outcome, to_recipient_id, to_recipient_candidate_id, input_request_id, confirmation_id, confirmation_view, approval_outcome, change_target, correction_selection_outcome, blocked_view, auth_context_id, auth_request_view, auth_status, auth_retry_outcome, auth_attempt</t>
+          <t>recipient_name_hint, recipient_resolution_outcome, recipient_selection_reason, recipient_selection_outcome, to_recipient_id, to_recipient_candidate_id, input_request_id, confirmation_id, confirmation_view, approval_outcome, change_target, option_selection_outcome, blocked_view, auth_context_id, auth_request_view, auth_status, auth_attempt</t>
         </is>
       </c>
       <c r="N105" s="3" t="inlineStr">
         <is>
-          <t>recipient_name_hint, recipient_resolution_outcome, recipient_selection_reason, recipient_selection_outcome, to_recipient_id, to_recipient_candidate_id, input_request_id, confirmation_id, confirmation_view, approval_outcome, change_target, correction_selection_outcome, blocked_view, auth_context_id, auth_request_view, auth_status, auth_retry_outcome, auth_attempt</t>
+          <t>recipient_name_hint, recipient_resolution_outcome, recipient_selection_reason, recipient_selection_outcome, to_recipient_id, to_recipient_candidate_id, input_request_id, confirmation_id, confirmation_view, approval_outcome, change_target, option_selection_outcome, blocked_view, auth_context_id, auth_request_view, auth_status, auth_attempt, option</t>
         </is>
       </c>
       <c r="O105" s="3" t="inlineStr">
@@ -9142,12 +9142,12 @@
       <c r="L106" s="3" t="inlineStr"/>
       <c r="M106" s="3" t="inlineStr">
         <is>
-          <t>amount, amount_input_outcome, input_request_id, confirmation_id, confirmation_view, approval_outcome, change_target, correction_selection_outcome, blocked_view, auth_context_id, auth_request_view, auth_status, auth_retry_outcome, auth_attempt</t>
+          <t>amount, amount_input_outcome, input_request_id, confirmation_id, confirmation_view, approval_outcome, change_target, option_selection_outcome, blocked_view, auth_context_id, auth_request_view, auth_status, auth_attempt</t>
         </is>
       </c>
       <c r="N106" s="3" t="inlineStr">
         <is>
-          <t>amount, amount_input_outcome, input_request_id, confirmation_id, confirmation_view, approval_outcome, change_target, correction_selection_outcome, blocked_view, auth_context_id, auth_request_view, auth_status, auth_retry_outcome, auth_attempt</t>
+          <t>amount, amount_input_outcome, input_request_id, confirmation_id, confirmation_view, approval_outcome, change_target, option_selection_outcome, blocked_view, auth_context_id, auth_request_view, auth_status, auth_attempt, option</t>
         </is>
       </c>
       <c r="O106" s="3" t="inlineStr">
@@ -9295,7 +9295,7 @@
       </c>
       <c r="N108" s="3" t="inlineStr">
         <is>
-          <t>correction_selection_outcome, change_target, input_request_id</t>
+          <t>option_selection_outcome, option, input_request_id</t>
         </is>
       </c>
       <c r="O108" s="3" t="inlineStr">
@@ -9362,12 +9362,12 @@
       <c r="L109" s="3" t="inlineStr"/>
       <c r="M109" s="3" t="inlineStr">
         <is>
-          <t>auth_context_id, auth_request_view, auth_status, auth_retry_outcome, auth_attempt</t>
+          <t>auth_context_id, auth_request_view, auth_status, option_selection_outcome, auth_attempt</t>
         </is>
       </c>
       <c r="N109" s="3" t="inlineStr">
         <is>
-          <t>auth_context_id, auth_request_view, auth_status, auth_retry_outcome, auth_attempt</t>
+          <t>auth_context_id, auth_request_view, auth_status, option_selection_outcome, auth_attempt</t>
         </is>
       </c>
       <c r="O109" s="3" t="inlineStr">
@@ -9607,7 +9607,7 @@
       </c>
       <c r="N112" s="3" t="inlineStr">
         <is>
-          <t>auth_retry_outcome, input_request_id</t>
+          <t>option_selection_outcome, input_request_id, option</t>
         </is>
       </c>
       <c r="O112" s="3" t="inlineStr">
@@ -24837,7 +24837,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>사용자가 수정할 본인송금 조건</t>
+          <t>사용자가 수정할 대상</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -24941,7 +24941,7 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>correction_selection_outcome</t>
+          <t>option_selection_outcome</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -24961,7 +24961,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>복수 수정 대상 선택 UI의 검증된 재개 결과</t>
+          <t>정정 대상 선택 또는 재인증 재시도 선택 UI의 검증된 재개 결과</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -24986,7 +24986,7 @@
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>selected, cancelled</t>
+          <t>selected</t>
         </is>
       </c>
     </row>
@@ -25251,37 +25251,37 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>auth_retry_outcome</t>
+          <t>prepare_attempt</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>재인증 선택 UI의 검증된 재개 결과</t>
+          <t>Prepare 멱등성 키 생성을 위한 논리 시도 번호</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>interaction</t>
+          <t>workflow</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>Route 결정, 재인증 또는 Workflow 종료</t>
+          <t>Workflow 종료</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
@@ -25296,7 +25296,7 @@
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>retry, cancelled</t>
+          <t>통신 재시도에서는 증가시키지 않음</t>
         </is>
       </c>
     </row>
@@ -25313,7 +25313,7 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>prepare_attempt</t>
+          <t>auth_attempt</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -25333,7 +25333,7 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>Prepare 멱등성 키 생성을 위한 논리 시도 번호</t>
+          <t>Auth Context와 송금 Execute 멱등성 키 생성을 위한 인증 시도 번호</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -25343,7 +25343,7 @@
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>Workflow 종료</t>
+          <t>입력 초기화 또는 Workflow 종료</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
@@ -25358,7 +25358,7 @@
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>통신 재시도에서는 증가시키지 않음</t>
+          <t>재인증에서만 증가하고 통신 재시도에서는 유지</t>
         </is>
       </c>
     </row>
@@ -25375,52 +25375,52 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>auth_attempt</t>
+          <t>transaction_id</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>null</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>Auth Context와 송금 Execute 멱등성 키 생성을 위한 인증 시도 번호</t>
+          <t>완료된 본인송금 거래 ID</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>workflow</t>
+          <t>result</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>입력 초기화 또는 Workflow 종료</t>
+          <t>결과 보존 정책에 따름</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>allow</t>
+          <t>masked</t>
         </is>
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>재인증에서만 증가하고 통신 재시도에서는 유지</t>
+          <t>Backend Execute 응답 기준</t>
         </is>
       </c>
     </row>
@@ -25437,12 +25437,12 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>transaction_id</t>
+          <t>completed_at</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -25457,7 +25457,7 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>완료된 본인송금 거래 ID</t>
+          <t>본인송금 완료 시각</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -25472,12 +25472,12 @@
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>masked</t>
+          <t>allow</t>
         </is>
       </c>
       <c r="L104" s="2" t="inlineStr">
@@ -25494,17 +25494,17 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>wf_internal_transfer</t>
+          <t>wf_external_transfer</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>completed_at</t>
+          <t>from_account_hint</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -25519,32 +25519,32 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>본인송금 완료 시각</t>
+          <t>사용자 발화에서 추출한 출금 계좌 힌트</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>result</t>
+          <t>workflow</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>결과 보존 정책에 따름</t>
+          <t>출금 계좌 초기화 또는 Workflow 종료</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>allow</t>
+          <t>masked</t>
         </is>
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>Backend Execute 응답 기준</t>
+          <t>은행명, 별칭 또는 계좌 유형 힌트</t>
         </is>
       </c>
     </row>
@@ -25561,7 +25561,7 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>from_account_hint</t>
+          <t>account_resolution_outcome</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -25581,32 +25581,32 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>사용자 발화에서 추출한 출금 계좌 힌트</t>
+          <t>Backend 출금 계좌 자동 확정 결과</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>workflow</t>
+          <t>interaction</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>출금 계좌 초기화 또는 Workflow 종료</t>
+          <t>계좌 확정·초기화 또는 Workflow 종료</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>masked</t>
+          <t>allow</t>
         </is>
       </c>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>은행명, 별칭 또는 계좌 유형 힌트</t>
+          <t>resolved, selection_required, no_accounts</t>
         </is>
       </c>
     </row>
@@ -25623,52 +25623,52 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>account_resolution_outcome</t>
+          <t>accounts</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>list[AccountCandidate]</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>Backend가 검증한 출금 계좌 선택 후보</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>interaction</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>계좌 확정·초기화 또는 Workflow 종료</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
           <t>true</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="G107" s="2" t="inlineStr">
-        <is>
-          <t>Backend 출금 계좌 자동 확정 결과</t>
-        </is>
-      </c>
-      <c r="H107" s="2" t="inlineStr">
-        <is>
-          <t>interaction</t>
-        </is>
-      </c>
-      <c r="I107" s="2" t="inlineStr">
-        <is>
-          <t>계좌 확정·초기화 또는 Workflow 종료</t>
-        </is>
-      </c>
-      <c r="J107" s="2" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>allow</t>
+          <t>exclude</t>
         </is>
       </c>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>resolved, selection_required, no_accounts</t>
+          <t>항상 최신 응답으로 교체</t>
         </is>
       </c>
     </row>
@@ -25685,52 +25685,52 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>accounts</t>
+          <t>account_selection_outcome</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>list[AccountCandidate]</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>출금 계좌 선택 UI 재개 결과</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>interaction</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>Route 결정·초기화 또는 Workflow 종료</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
           <t>false</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G108" s="2" t="inlineStr">
-        <is>
-          <t>Backend가 검증한 출금 계좌 선택 후보</t>
-        </is>
-      </c>
-      <c r="H108" s="2" t="inlineStr">
-        <is>
-          <t>interaction</t>
-        </is>
-      </c>
-      <c r="I108" s="2" t="inlineStr">
-        <is>
-          <t>계좌 확정·초기화 또는 Workflow 종료</t>
-        </is>
-      </c>
-      <c r="J108" s="2" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>exclude</t>
+          <t>allow</t>
         </is>
       </c>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>항상 최신 응답으로 교체</t>
+          <t>selected, cancelled</t>
         </is>
       </c>
     </row>
@@ -25747,7 +25747,7 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>account_selection_outcome</t>
+          <t>from_account_id</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
@@ -25767,32 +25767,32 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>출금 계좌 선택 UI 재개 결과</t>
+          <t>송금액을 출금할 검증된 사용자 계좌 ID</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>interaction</t>
+          <t>workflow</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>Route 결정·초기화 또는 Workflow 종료</t>
+          <t>출금 계좌 초기화 또는 Workflow 종료</t>
         </is>
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t>allow</t>
+          <t>masked</t>
         </is>
       </c>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>selected, cancelled</t>
+          <t>account_ids 배열에서 정확히 한 값을 저장</t>
         </is>
       </c>
     </row>
@@ -25809,7 +25809,7 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>from_account_id</t>
+          <t>recipient_name_hint</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -25829,7 +25829,7 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>송금액을 출금할 검증된 사용자 계좌 ID</t>
+          <t>최초 발화에서 추출한 수취인 이름 힌트</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -25839,7 +25839,7 @@
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>출금 계좌 초기화 또는 Workflow 종료</t>
+          <t>수취인 초기화 또는 Workflow 종료</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
@@ -25854,7 +25854,7 @@
       </c>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>account_ids 배열에서 정확히 한 값을 저장</t>
+          <t>기존 완료 타인송금 거래 자동 확정에만 사용</t>
         </is>
       </c>
     </row>
@@ -25871,7 +25871,7 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>recipient_name_hint</t>
+          <t>recipient_resolution_outcome</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
@@ -25891,32 +25891,32 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>최초 발화에서 추출한 수취인 이름 힌트</t>
+          <t>기존 거래 수취인 자동 확정 결과</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>workflow</t>
+          <t>interaction</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>수취인 초기화 또는 Workflow 종료</t>
+          <t>수취인 확정·초기화 또는 Workflow 종료</t>
         </is>
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>masked</t>
+          <t>allow</t>
         </is>
       </c>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t>기존 완료 타인송금 거래 자동 확정에만 사용</t>
+          <t>resolved, selection_required</t>
         </is>
       </c>
     </row>
@@ -25933,7 +25933,7 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>recipient_resolution_outcome</t>
+          <t>recipient_selection_reason</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
@@ -25953,7 +25953,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>기존 거래 수취인 자동 확정 결과</t>
+          <t>수취인 선택 UI가 필요한 사유</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -25978,7 +25978,7 @@
       </c>
       <c r="L112" s="2" t="inlineStr">
         <is>
-          <t>resolved, selection_required</t>
+          <t>multiple_matches, no_match</t>
         </is>
       </c>
     </row>
@@ -25995,7 +25995,7 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>recipient_selection_reason</t>
+          <t>recipient_selection_outcome</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
@@ -26015,7 +26015,7 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>수취인 선택 UI가 필요한 사유</t>
+          <t>수취인 선택 UI 재개 결과</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -26025,7 +26025,7 @@
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>수취인 확정·초기화 또는 Workflow 종료</t>
+          <t>Route 결정·초기화 또는 Workflow 종료</t>
         </is>
       </c>
       <c r="J113" s="2" t="inlineStr">
@@ -26040,7 +26040,7 @@
       </c>
       <c r="L113" s="2" t="inlineStr">
         <is>
-          <t>multiple_matches, no_match</t>
+          <t>selected, cancelled</t>
         </is>
       </c>
     </row>
@@ -26057,7 +26057,7 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>recipient_selection_outcome</t>
+          <t>to_recipient_id</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
@@ -26077,32 +26077,32 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>수취인 선택 UI 재개 결과</t>
+          <t>Backend가 검증한 기존 수취인 ID</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>interaction</t>
+          <t>workflow</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>Route 결정·초기화 또는 Workflow 종료</t>
+          <t>수취인 초기화 또는 Workflow 종료</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>allow</t>
+          <t>masked</t>
         </is>
       </c>
       <c r="L114" s="2" t="inlineStr">
         <is>
-          <t>selected, cancelled</t>
+          <t>신규 후보 ID와 동시에 존재할 수 없음</t>
         </is>
       </c>
     </row>
@@ -26119,7 +26119,7 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>to_recipient_id</t>
+          <t>to_recipient_candidate_id</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
@@ -26139,7 +26139,7 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>Backend가 검증한 기존 수취인 ID</t>
+          <t>Backend가 신규 계좌 검증 후 발급한 수취인 후보 ID</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
@@ -26164,7 +26164,7 @@
       </c>
       <c r="L115" s="2" t="inlineStr">
         <is>
-          <t>신규 후보 ID와 동시에 존재할 수 없음</t>
+          <t>계좌번호 원문은 저장하지 않음</t>
         </is>
       </c>
     </row>
@@ -26181,12 +26181,12 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>to_recipient_candidate_id</t>
+          <t>amount</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -26201,7 +26201,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>Backend가 신규 계좌 검증 후 발급한 수취인 후보 ID</t>
+          <t>KRW 최소 화폐 단위의 송금 금액</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -26211,7 +26211,7 @@
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>수취인 초기화 또는 Workflow 종료</t>
+          <t>금액 초기화 또는 Workflow 종료</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
@@ -26221,12 +26221,12 @@
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>masked</t>
+          <t>exclude</t>
         </is>
       </c>
       <c r="L116" s="2" t="inlineStr">
         <is>
-          <t>계좌번호 원문은 저장하지 않음</t>
+          <t>Agent는 정수이고 0보다 큰지만 확인</t>
         </is>
       </c>
     </row>
@@ -26243,12 +26243,12 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>amount</t>
+          <t>amount_input_outcome</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
@@ -26263,32 +26263,32 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>KRW 최소 화폐 단위의 송금 금액</t>
+          <t>금액 입력 UI 재개 결과</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>workflow</t>
+          <t>interaction</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>금액 초기화 또는 Workflow 종료</t>
+          <t>Route 결정·초기화 또는 Workflow 종료</t>
         </is>
       </c>
       <c r="J117" s="2" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
-          <t>exclude</t>
+          <t>allow</t>
         </is>
       </c>
       <c r="L117" s="2" t="inlineStr">
         <is>
-          <t>Agent는 정수이고 0보다 큰지만 확인</t>
+          <t>submitted, cancelled</t>
         </is>
       </c>
     </row>
@@ -26305,7 +26305,7 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>amount_input_outcome</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
@@ -26315,27 +26315,27 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>금액 입력 UI 재개 결과</t>
+          <t>타인송금 통화</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>interaction</t>
+          <t>workflow</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>Route 결정·초기화 또는 Workflow 종료</t>
+          <t>Workflow 종료</t>
         </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
@@ -26350,7 +26350,7 @@
       </c>
       <c r="L118" s="2" t="inlineStr">
         <is>
-          <t>submitted, cancelled</t>
+          <t>현재 KRW만 허용</t>
         </is>
       </c>
     </row>
@@ -26367,7 +26367,7 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>input_request_id</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
@@ -26377,42 +26377,42 @@
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>null</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>타인송금 통화</t>
+          <t>수취인·계좌·금액·수정 입력과 재개를 연결하는 식별자</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>workflow</t>
+          <t>interaction</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>Workflow 종료</t>
+          <t>재개 검증·초기화 또는 Workflow 종료</t>
         </is>
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
-          <t>allow</t>
+          <t>masked</t>
         </is>
       </c>
       <c r="L119" s="2" t="inlineStr">
         <is>
-          <t>현재 KRW만 허용</t>
+          <t>입력 대기 중에만 보존</t>
         </is>
       </c>
     </row>
@@ -26429,7 +26429,7 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>input_request_id</t>
+          <t>confirmation_id</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
@@ -26449,17 +26449,17 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>수취인·계좌·금액·수정 입력과 재개를 연결하는 식별자</t>
+          <t>Backend가 발급한 타인송금 승인 식별자</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>interaction</t>
+          <t>workflow</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>재개 검증·초기화 또는 Workflow 종료</t>
+          <t>입력 초기화·실행 완료 또는 Workflow 종료</t>
         </is>
       </c>
       <c r="J120" s="2" t="inlineStr">
@@ -26474,7 +26474,7 @@
       </c>
       <c r="L120" s="2" t="inlineStr">
         <is>
-          <t>입력 대기 중에만 보존</t>
+          <t>Prepare에서 고정한 송금 조건 참조</t>
         </is>
       </c>
     </row>
@@ -26491,12 +26491,12 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>confirmation_id</t>
+          <t>confirmation_view</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>ConfirmationView</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
@@ -26511,7 +26511,7 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>Backend가 발급한 타인송금 승인 식별자</t>
+          <t>승인 화면과 완료 결과에서 재사용할 Backend 표시 데이터</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -26521,7 +26521,7 @@
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>입력 초기화·실행 완료 또는 Workflow 종료</t>
+          <t>입력 초기화·결과 전송 또는 Workflow 종료</t>
         </is>
       </c>
       <c r="J121" s="2" t="inlineStr">
@@ -26531,12 +26531,12 @@
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
-          <t>masked</t>
+          <t>exclude</t>
         </is>
       </c>
       <c r="L121" s="2" t="inlineStr">
         <is>
-          <t>Prepare에서 고정한 송금 조건 참조</t>
+          <t>마스킹 계좌·수취인, 금액과 통화 포함</t>
         </is>
       </c>
     </row>
@@ -26553,12 +26553,12 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>confirmation_view</t>
+          <t>approval_outcome</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>ConfirmationView</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -26573,32 +26573,32 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>승인 화면과 완료 결과에서 재사용할 Backend 표시 데이터</t>
+          <t>Backend가 검증한 승인 재개 결과</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>workflow</t>
+          <t>interaction</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>입력 초기화·결과 전송 또는 Workflow 종료</t>
+          <t>Route 결정·초기화 또는 Workflow 종료</t>
         </is>
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>exclude</t>
+          <t>allow</t>
         </is>
       </c>
       <c r="L122" s="2" t="inlineStr">
         <is>
-          <t>마스킹 계좌·수취인, 금액과 통화 포함</t>
+          <t>approved, change_requested, cancelled</t>
         </is>
       </c>
     </row>
@@ -26615,7 +26615,7 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>approval_outcome</t>
+          <t>change_target</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
@@ -26635,7 +26635,7 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>Backend가 검증한 승인 재개 결과</t>
+          <t>사용자가 수정할 대상</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
@@ -26645,7 +26645,7 @@
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>Route 결정·초기화 또는 Workflow 종료</t>
+          <t>수정 Route·초기화 또는 Workflow 종료</t>
         </is>
       </c>
       <c r="J123" s="2" t="inlineStr">
@@ -26660,7 +26660,7 @@
       </c>
       <c r="L123" s="2" t="inlineStr">
         <is>
-          <t>approved, change_requested, cancelled</t>
+          <t>from_account, recipient, amount</t>
         </is>
       </c>
     </row>
@@ -26677,12 +26677,12 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>change_target</t>
+          <t>correction_view</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>TransferCorrectionView</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
@@ -26697,7 +26697,7 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>사용자가 수정할 타인송금 조건</t>
+          <t>Backend가 반환한 수정 가능 대상과 표시 사유</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
@@ -26707,22 +26707,22 @@
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>수정 Route·초기화 또는 Workflow 종료</t>
+          <t>새 Prepare 시작 또는 Workflow 종료</t>
         </is>
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>allow</t>
+          <t>exclude</t>
         </is>
       </c>
       <c r="L124" s="2" t="inlineStr">
         <is>
-          <t>from_account, recipient, amount</t>
+          <t>다음 입력 UI까지 유지</t>
         </is>
       </c>
     </row>
@@ -26739,12 +26739,12 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>correction_view</t>
+          <t>option_selection_outcome</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>TransferCorrectionView</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
@@ -26759,7 +26759,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>Backend가 반환한 수정 가능 대상과 표시 사유</t>
+          <t>정정 대상 선택 또는 재인증 재시도 선택 UI의 검증된 재개 결과</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -26769,22 +26769,22 @@
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>새 Prepare 시작 또는 Workflow 종료</t>
+          <t>수정 Route·초기화 또는 Workflow 종료</t>
         </is>
       </c>
       <c r="J125" s="2" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
-          <t>exclude</t>
+          <t>allow</t>
         </is>
       </c>
       <c r="L125" s="2" t="inlineStr">
         <is>
-          <t>다음 입력 UI까지 유지</t>
+          <t>selected</t>
         </is>
       </c>
     </row>
@@ -26801,12 +26801,12 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>correction_selection_outcome</t>
+          <t>blocked_view</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>BlockedView</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
@@ -26821,7 +26821,7 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>복수 수정 대상 선택 UI 재개 결과</t>
+          <t>Backend 사용자 표시용 송금 차단 안내</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
@@ -26831,22 +26831,22 @@
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>수정 Route·초기화 또는 Workflow 종료</t>
+          <t>차단 결과 전송 또는 Workflow 종료</t>
         </is>
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>allow</t>
+          <t>exclude</t>
         </is>
       </c>
       <c r="L126" s="2" t="inlineStr">
         <is>
-          <t>selected, cancelled</t>
+          <t>Agent가 내부 정책 사유를 해석하지 않음</t>
         </is>
       </c>
     </row>
@@ -26863,12 +26863,12 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>blocked_view</t>
+          <t>auth_context_id</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>BlockedView</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
@@ -26883,17 +26883,17 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Backend 사용자 표시용 송금 차단 안내</t>
+          <t>Backend가 발급한 추가 인증 Context ID</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>interaction</t>
+          <t>workflow</t>
         </is>
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
-          <t>차단 결과 전송 또는 Workflow 종료</t>
+          <t>재인증·입력 초기화·실행 완료 또는 Workflow 종료</t>
         </is>
       </c>
       <c r="J127" s="2" t="inlineStr">
@@ -26903,12 +26903,12 @@
       </c>
       <c r="K127" s="2" t="inlineStr">
         <is>
-          <t>exclude</t>
+          <t>masked</t>
         </is>
       </c>
       <c r="L127" s="2" t="inlineStr">
         <is>
-          <t>Agent가 내부 정책 사유를 해석하지 않음</t>
+          <t>인증 원문은 저장하지 않음</t>
         </is>
       </c>
     </row>
@@ -26925,12 +26925,12 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>auth_context_id</t>
+          <t>auth_request_view</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>AuthRequestView</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
@@ -26945,17 +26945,17 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>Backend가 발급한 추가 인증 Context ID</t>
+          <t>인증 UI에 표시할 Backend 제공 데이터</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>workflow</t>
+          <t>interaction</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>재인증·입력 초기화·실행 완료 또는 Workflow 종료</t>
+          <t>인증 결과·재인증 또는 Workflow 종료</t>
         </is>
       </c>
       <c r="J128" s="2" t="inlineStr">
@@ -26965,12 +26965,12 @@
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>masked</t>
+          <t>exclude</t>
         </is>
       </c>
       <c r="L128" s="2" t="inlineStr">
         <is>
-          <t>인증 원문은 저장하지 않음</t>
+          <t>인증 방식과 만료 시각 포함</t>
         </is>
       </c>
     </row>
@@ -26987,12 +26987,12 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>auth_request_view</t>
+          <t>auth_status</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>AuthRequestView</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
@@ -27007,7 +27007,7 @@
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>인증 UI에 표시할 Backend 제공 데이터</t>
+          <t>Backend가 검증한 추가 인증 결과</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
@@ -27017,22 +27017,22 @@
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>인증 결과·재인증 또는 Workflow 종료</t>
+          <t>Route 결정·재인증 또는 Workflow 종료</t>
         </is>
       </c>
       <c r="J129" s="2" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="K129" s="2" t="inlineStr">
         <is>
-          <t>exclude</t>
+          <t>allow</t>
         </is>
       </c>
       <c r="L129" s="2" t="inlineStr">
         <is>
-          <t>인증 방식과 만료 시각 포함</t>
+          <t>verified, failed, cancelled, expired</t>
         </is>
       </c>
     </row>
@@ -27049,37 +27049,37 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>auth_status</t>
+          <t>prepare_attempt</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>Backend가 검증한 추가 인증 결과</t>
+          <t>Prepare 멱등성 키 논리 시도 번호</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>interaction</t>
+          <t>workflow</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>Route 결정·재인증 또는 Workflow 종료</t>
+          <t>Workflow 종료</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr">
@@ -27094,7 +27094,7 @@
       </c>
       <c r="L130" s="2" t="inlineStr">
         <is>
-          <t>verified, failed, cancelled, expired</t>
+          <t>통신 재시도에서는 증가시키지 않음</t>
         </is>
       </c>
     </row>
@@ -27111,37 +27111,37 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>auth_retry_outcome</t>
+          <t>auth_attempt</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>재인증 선택 UI 재개 결과</t>
+          <t>Auth Context와 Execute 멱등성 키 인증 시도 번호</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>interaction</t>
+          <t>workflow</t>
         </is>
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>Route 결정·재인증 또는 Workflow 종료</t>
+          <t>입력 초기화 또는 Workflow 종료</t>
         </is>
       </c>
       <c r="J131" s="2" t="inlineStr">
@@ -27156,7 +27156,7 @@
       </c>
       <c r="L131" s="2" t="inlineStr">
         <is>
-          <t>retry, cancelled</t>
+          <t>재인증에서만 증가</t>
         </is>
       </c>
     </row>
@@ -27173,52 +27173,52 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>prepare_attempt</t>
+          <t>transaction_id</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>null</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>Prepare 멱등성 키 논리 시도 번호</t>
+          <t>완료된 타인송금 거래 ID</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>workflow</t>
+          <t>result</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>Workflow 종료</t>
+          <t>결과 보존 정책에 따름</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>allow</t>
+          <t>masked</t>
         </is>
       </c>
       <c r="L132" s="2" t="inlineStr">
         <is>
-          <t>통신 재시도에서는 증가시키지 않음</t>
+          <t>Backend Execute 응답 기준</t>
         </is>
       </c>
     </row>
@@ -27235,176 +27235,176 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>auth_attempt</t>
+          <t>completed_at</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>타인송금 완료 시각</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>result</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>결과 보존 정책에 따름</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
           <t>false</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G133" s="2" t="inlineStr">
-        <is>
-          <t>Auth Context와 Execute 멱등성 키 인증 시도 번호</t>
-        </is>
-      </c>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="K133" s="2" t="inlineStr">
+        <is>
+          <t>allow</t>
+        </is>
+      </c>
+      <c r="L133" s="2" t="inlineStr">
+        <is>
+          <t>Backend Execute 응답 기준</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
         <is>
           <t>workflow</t>
         </is>
       </c>
-      <c r="I133" s="2" t="inlineStr">
-        <is>
-          <t>입력 초기화 또는 Workflow 종료</t>
-        </is>
-      </c>
-      <c r="J133" s="2" t="inlineStr">
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>wf_external_transfer</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>option</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>정정 대상 선택 또는 재인증 선택(retry/cancel) UI의 선택값</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>interaction</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>수정 Route·재인증 또는 Workflow 종료</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="K133" s="2" t="inlineStr">
+      <c r="K134" t="inlineStr">
         <is>
           <t>allow</t>
         </is>
       </c>
-      <c r="L133" s="2" t="inlineStr">
-        <is>
-          <t>재인증에서만 증가</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>from_account, recipient, amount, retry, cancel</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
         <is>
           <t>workflow</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>wf_external_transfer</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>transaction_id</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>wf_internal_transfer</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>option</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E135" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F135" t="inlineStr">
         <is>
           <t>null</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr">
-        <is>
-          <t>완료된 타인송금 거래 ID</t>
-        </is>
-      </c>
-      <c r="H134" s="2" t="inlineStr">
-        <is>
-          <t>result</t>
-        </is>
-      </c>
-      <c r="I134" s="2" t="inlineStr">
-        <is>
-          <t>결과 보존 정책에 따름</t>
-        </is>
-      </c>
-      <c r="J134" s="2" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="K134" s="2" t="inlineStr">
-        <is>
-          <t>masked</t>
-        </is>
-      </c>
-      <c r="L134" s="2" t="inlineStr">
-        <is>
-          <t>Backend Execute 응답 기준</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
-        <is>
-          <t>workflow</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>wf_external_transfer</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>completed_at</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
-        <is>
-          <t>datetime</t>
-        </is>
-      </c>
-      <c r="E135" s="2" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="F135" s="2" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="G135" s="2" t="inlineStr">
-        <is>
-          <t>타인송금 완료 시각</t>
-        </is>
-      </c>
-      <c r="H135" s="2" t="inlineStr">
-        <is>
-          <t>result</t>
-        </is>
-      </c>
-      <c r="I135" s="2" t="inlineStr">
-        <is>
-          <t>결과 보존 정책에 따름</t>
-        </is>
-      </c>
-      <c r="J135" s="2" t="inlineStr">
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>정정 대상 선택 또는 재인증 선택(retry/cancel) UI의 선택값</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>interaction</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>수정 Route·재인증 또는 Workflow 종료</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="K135" s="2" t="inlineStr">
+      <c r="K135" t="inlineStr">
         <is>
           <t>allow</t>
         </is>
       </c>
-      <c r="L135" s="2" t="inlineStr">
-        <is>
-          <t>Backend Execute 응답 기준</t>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>from_account, to_account, amount, retry, cancel</t>
         </is>
       </c>
     </row>
@@ -27437,7 +27437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I460"/>
+  <dimension ref="A1:I468"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -38474,12 +38474,12 @@
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>correction_selection_outcome</t>
+          <t>option_selection_outcome</t>
         </is>
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>resume.value.correction_selection_outcome</t>
+          <t>resume.value.option_selection_outcome</t>
         </is>
       </c>
       <c r="F244" s="2" t="inlineStr">
@@ -38517,12 +38517,12 @@
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>change_target</t>
+          <t>option</t>
         </is>
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
-          <t>resume.value.change_target</t>
+          <t>resume.value.option</t>
         </is>
       </c>
       <c r="F245" s="2" t="inlineStr">
@@ -38693,12 +38693,12 @@
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>auth_retry_outcome</t>
+          <t>option_selection_outcome</t>
         </is>
       </c>
       <c r="E249" s="2" t="inlineStr">
         <is>
-          <t>agent.state.auth_retry_outcome=null</t>
+          <t>agent.state.option_selection_outcome=null</t>
         </is>
       </c>
       <c r="F249" s="2" t="inlineStr">
@@ -39174,12 +39174,12 @@
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>auth_retry_outcome</t>
+          <t>option_selection_outcome</t>
         </is>
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
-          <t>resume.value.auth_retry_outcome</t>
+          <t>resume.value.option_selection_outcome</t>
         </is>
       </c>
       <c r="F260" s="2" t="inlineStr">
@@ -40372,12 +40372,12 @@
       </c>
       <c r="D286" s="2" t="inlineStr">
         <is>
-          <t>correction_selection_outcome</t>
+          <t>option_selection_outcome</t>
         </is>
       </c>
       <c r="E286" s="2" t="inlineStr">
         <is>
-          <t>agent.state.correction_selection_outcome=null</t>
+          <t>agent.state.option_selection_outcome=null</t>
         </is>
       </c>
       <c r="F286" s="2" t="inlineStr">
@@ -40607,12 +40607,12 @@
       </c>
       <c r="D291" s="2" t="inlineStr">
         <is>
-          <t>auth_retry_outcome</t>
+          <t>option_selection_outcome</t>
         </is>
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
-          <t>agent.state.auth_retry_outcome=null</t>
+          <t>agent.state.option_selection_outcome=null</t>
         </is>
       </c>
       <c r="F291" s="2" t="inlineStr">
@@ -41218,12 +41218,12 @@
       </c>
       <c r="D304" s="2" t="inlineStr">
         <is>
-          <t>correction_selection_outcome</t>
+          <t>option_selection_outcome</t>
         </is>
       </c>
       <c r="E304" s="2" t="inlineStr">
         <is>
-          <t>agent.state.correction_selection_outcome=null</t>
+          <t>agent.state.option_selection_outcome=null</t>
         </is>
       </c>
       <c r="F304" s="2" t="inlineStr">
@@ -41453,12 +41453,12 @@
       </c>
       <c r="D309" s="2" t="inlineStr">
         <is>
-          <t>auth_retry_outcome</t>
+          <t>option_selection_outcome</t>
         </is>
       </c>
       <c r="E309" s="2" t="inlineStr">
         <is>
-          <t>agent.state.auth_retry_outcome=null</t>
+          <t>agent.state.option_selection_outcome=null</t>
         </is>
       </c>
       <c r="F309" s="2" t="inlineStr">
@@ -41876,12 +41876,12 @@
       </c>
       <c r="D318" s="2" t="inlineStr">
         <is>
-          <t>correction_selection_outcome</t>
+          <t>option_selection_outcome</t>
         </is>
       </c>
       <c r="E318" s="2" t="inlineStr">
         <is>
-          <t>agent.state.correction_selection_outcome=null</t>
+          <t>agent.state.option_selection_outcome=null</t>
         </is>
       </c>
       <c r="F318" s="2" t="inlineStr">
@@ -42111,12 +42111,12 @@
       </c>
       <c r="D323" s="2" t="inlineStr">
         <is>
-          <t>auth_retry_outcome</t>
+          <t>option_selection_outcome</t>
         </is>
       </c>
       <c r="E323" s="2" t="inlineStr">
         <is>
-          <t>agent.state.auth_retry_outcome=null</t>
+          <t>agent.state.option_selection_outcome=null</t>
         </is>
       </c>
       <c r="F323" s="2" t="inlineStr">
@@ -44411,12 +44411,12 @@
       </c>
       <c r="D375" s="2" t="inlineStr">
         <is>
-          <t>correction_selection_outcome</t>
+          <t>option_selection_outcome</t>
         </is>
       </c>
       <c r="E375" s="2" t="inlineStr">
         <is>
-          <t>resume.value.correction_selection_outcome</t>
+          <t>resume.value.option_selection_outcome</t>
         </is>
       </c>
       <c r="F375" s="2" t="inlineStr">
@@ -44454,12 +44454,12 @@
       </c>
       <c r="D376" s="2" t="inlineStr">
         <is>
-          <t>change_target</t>
+          <t>option</t>
         </is>
       </c>
       <c r="E376" s="2" t="inlineStr">
         <is>
-          <t>resume.value.change_target</t>
+          <t>resume.value.option</t>
         </is>
       </c>
       <c r="F376" s="2" t="inlineStr">
@@ -44626,12 +44626,12 @@
       </c>
       <c r="D380" s="2" t="inlineStr">
         <is>
-          <t>auth_retry_outcome</t>
+          <t>option_selection_outcome</t>
         </is>
       </c>
       <c r="E380" s="2" t="inlineStr">
         <is>
-          <t>agent.state.auth_retry_outcome=null</t>
+          <t>agent.state.option_selection_outcome=null</t>
         </is>
       </c>
       <c r="F380" s="2" t="inlineStr">
@@ -45103,12 +45103,12 @@
       </c>
       <c r="D391" s="2" t="inlineStr">
         <is>
-          <t>auth_retry_outcome</t>
+          <t>option_selection_outcome</t>
         </is>
       </c>
       <c r="E391" s="2" t="inlineStr">
         <is>
-          <t>resume.value.auth_retry_outcome</t>
+          <t>resume.value.option_selection_outcome</t>
         </is>
       </c>
       <c r="F391" s="2" t="inlineStr">
@@ -46285,12 +46285,12 @@
       </c>
       <c r="D417" s="2" t="inlineStr">
         <is>
-          <t>correction_selection_outcome</t>
+          <t>option_selection_outcome</t>
         </is>
       </c>
       <c r="E417" s="2" t="inlineStr">
         <is>
-          <t>agent.state.correction_selection_outcome=null</t>
+          <t>agent.state.option_selection_outcome=null</t>
         </is>
       </c>
       <c r="F417" s="2" t="inlineStr">
@@ -46520,12 +46520,12 @@
       </c>
       <c r="D422" s="2" t="inlineStr">
         <is>
-          <t>auth_retry_outcome</t>
+          <t>option_selection_outcome</t>
         </is>
       </c>
       <c r="E422" s="2" t="inlineStr">
         <is>
-          <t>agent.state.auth_retry_outcome=null</t>
+          <t>agent.state.option_selection_outcome=null</t>
         </is>
       </c>
       <c r="F422" s="2" t="inlineStr">
@@ -47131,12 +47131,12 @@
       </c>
       <c r="D435" s="2" t="inlineStr">
         <is>
-          <t>correction_selection_outcome</t>
+          <t>option_selection_outcome</t>
         </is>
       </c>
       <c r="E435" s="2" t="inlineStr">
         <is>
-          <t>agent.state.correction_selection_outcome=null</t>
+          <t>agent.state.option_selection_outcome=null</t>
         </is>
       </c>
       <c r="F435" s="2" t="inlineStr">
@@ -47366,12 +47366,12 @@
       </c>
       <c r="D440" s="2" t="inlineStr">
         <is>
-          <t>auth_retry_outcome</t>
+          <t>option_selection_outcome</t>
         </is>
       </c>
       <c r="E440" s="2" t="inlineStr">
         <is>
-          <t>agent.state.auth_retry_outcome=null</t>
+          <t>agent.state.option_selection_outcome=null</t>
         </is>
       </c>
       <c r="F440" s="2" t="inlineStr">
@@ -47789,12 +47789,12 @@
       </c>
       <c r="D449" s="2" t="inlineStr">
         <is>
-          <t>correction_selection_outcome</t>
+          <t>option_selection_outcome</t>
         </is>
       </c>
       <c r="E449" s="2" t="inlineStr">
         <is>
-          <t>agent.state.correction_selection_outcome=null</t>
+          <t>agent.state.option_selection_outcome=null</t>
         </is>
       </c>
       <c r="F449" s="2" t="inlineStr">
@@ -48024,12 +48024,12 @@
       </c>
       <c r="D454" s="2" t="inlineStr">
         <is>
-          <t>auth_retry_outcome</t>
+          <t>option_selection_outcome</t>
         </is>
       </c>
       <c r="E454" s="2" t="inlineStr">
         <is>
-          <t>agent.state.auth_retry_outcome=null</t>
+          <t>agent.state.option_selection_outcome=null</t>
         </is>
       </c>
       <c r="F454" s="2" t="inlineStr">
@@ -48330,6 +48330,326 @@
         </is>
       </c>
       <c r="I460" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>wf_external_transfer</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>request_external_auth_retry</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>output</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>option</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>resume.value.option</t>
+        </is>
+      </c>
+      <c r="F461" t="b">
+        <v>1</v>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>선택한 옵션(retry/cancel)을 저장한다.</t>
+        </is>
+      </c>
+      <c r="I461" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>wf_internal_transfer</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>request_internal_auth_retry</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>output</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>option</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>resume.value.option</t>
+        </is>
+      </c>
+      <c r="F462" t="b">
+        <v>1</v>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>선택한 옵션(retry/cancel)을 저장한다.</t>
+        </is>
+      </c>
+      <c r="I462" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>wf_internal_transfer</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>reset_internal_from_account</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>output</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>option</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>agent.state.option=null</t>
+        </is>
+      </c>
+      <c r="F463" t="b">
+        <v>1</v>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>정정 완료·초기화 시 정정 대상 선택값을 지운다.</t>
+        </is>
+      </c>
+      <c r="I463" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>wf_internal_transfer</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>reset_internal_to_account</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>output</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>option</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>agent.state.option=null</t>
+        </is>
+      </c>
+      <c r="F464" t="b">
+        <v>1</v>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>정정 완료·초기화 시 정정 대상 선택값을 지운다.</t>
+        </is>
+      </c>
+      <c r="I464" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>wf_internal_transfer</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>reset_internal_transfer_amount</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>output</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>option</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>agent.state.option=null</t>
+        </is>
+      </c>
+      <c r="F465" t="b">
+        <v>1</v>
+      </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>정정 완료·초기화 시 정정 대상 선택값을 지운다.</t>
+        </is>
+      </c>
+      <c r="I465" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>wf_external_transfer</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>reset_external_from_account</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>output</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>option</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>agent.state.option=null</t>
+        </is>
+      </c>
+      <c r="F466" t="b">
+        <v>1</v>
+      </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>정정 완료·초기화 시 정정 대상 선택값을 지운다.</t>
+        </is>
+      </c>
+      <c r="I466" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>wf_external_transfer</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>reset_external_recipient</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>output</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>option</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>agent.state.option=null</t>
+        </is>
+      </c>
+      <c r="F467" t="b">
+        <v>1</v>
+      </c>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>정정 완료·초기화 시 정정 대상 선택값을 지운다.</t>
+        </is>
+      </c>
+      <c r="I467" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>wf_external_transfer</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>reset_external_transfer_amount</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>output</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>option</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>agent.state.option=null</t>
+        </is>
+      </c>
+      <c r="F468" t="b">
+        <v>1</v>
+      </c>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>정정 완료·초기화 시 정정 대상 선택값을 지운다.</t>
+        </is>
+      </c>
+      <c r="I468" t="inlineStr">
         <is>
           <t>OK</t>
         </is>

--- a/agent/docs/agent-management-sheet-v3.xlsx
+++ b/agent/docs/agent-management-sheet-v3.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Workflow Catalog" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Workflow Steps" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Workflow Routes" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Workflow Data Schema" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Step Data Mapping" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contract Registry" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contract Mapping" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enum Registry" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Workflow Catalog" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Workflow Steps" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Workflow Routes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Workflow Data Schema" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Step Data Mapping" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Contract Registry" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Contract Mapping" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Enum Registry" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workflow Catalog'!$A$1:$L$10</definedName>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>생활비 통장에서 저축 통장으로 10만 원 옮겨줘</t>
+          <t>생활비 통장에서 저축 통장으로 10만 원 옮겨줘 | 내 계좌끼리 5만 원 송금해줘</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
